--- a/src/app/modules/dashboard/excel_files/whole-food-plant-based-hot-and-spicy-recipes.xlsx
+++ b/src/app/modules/dashboard/excel_files/whole-food-plant-based-hot-and-spicy-recipes.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7672,7 +7672,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9940,7 +9940,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
+          <t>['weight-loss', 'plant-based', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'soups', 'stews', 'stir-fry', 'wraps', 'bowls', 'salads', 'snacks']</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>whole_food</t>
+          <t>plant_based</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
